--- a/Result/profitability/1259.xlsx
+++ b/Result/profitability/1259.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:AM68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.59</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6325</v>
+        <v>0.86125</v>
       </c>
       <c r="N2" t="n">
-        <v>22.77</v>
+        <v>22.91375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.91875</v>
+        <v>1.185</v>
       </c>
       <c r="N3" t="n">
-        <v>23.29</v>
+        <v>23.5375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>98.40000000000001</v>
@@ -899,10 +899,10 @@
         <v>4.03</v>
       </c>
       <c r="M4" t="n">
-        <v>1.44375</v>
+        <v>1.655</v>
       </c>
       <c r="N4" t="n">
-        <v>23.96125</v>
+        <v>24.165</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.61</v>
       </c>
       <c r="M5" t="n">
-        <v>1.73625</v>
+        <v>1.89875</v>
       </c>
       <c r="N5" t="n">
-        <v>24.73875</v>
+        <v>24.8925</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8125</v>
+        <v>2.045</v>
       </c>
       <c r="N6" t="n">
-        <v>25.27375</v>
+        <v>25.39625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -8941,6 +8941,133 @@
       </c>
       <c r="AM67" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1569</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1198</v>
+      </c>
+      <c r="E68" t="n">
+        <v>371</v>
+      </c>
+      <c r="F68" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>67</v>
+      </c>
+      <c r="J68" t="n">
+        <v>65</v>
+      </c>
+      <c r="K68" t="n">
+        <v>63</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.55375</v>
+      </c>
+      <c r="N68" t="n">
+        <v>22.58125</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X68" t="n">
+        <v>31.66666666666666</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0.879999999999999</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.03866432337434089</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.96969696969697</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.05488621151271755</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK68" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
